--- a/gems-outputs/CC_セクション5.xlsx
+++ b/gems-outputs/CC_セクション5.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,7 +32,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -55,12 +59,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -901,12 +904,12 @@
           <t>切替</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>・スライド「表紙」を表示する。・講師は笑顔で画面中央に向かって立つ。</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>セクション5へようこそ。皆さん、ここまで進んでこられたこと、本当に素晴らしいです。今日からはいよいよ、開発者の世界で当たり前のように使われているGitHubという仕組みを学んでいきます。名前は聞いたことがある方も多いかもしれません。でも、実際に使ったことはない、何ができるかよくわからない、そういう方も多いはずです。安心してください。この動画では、GitHubをゼロから丁寧に解説します。10分後には、アカウントを作成して、リポジトリとコミットという2つの重要な概念を理解している状態になっているはずです。一緒に進めていきましょう。</t>
         </is>
@@ -933,12 +936,12 @@
           <t>導入</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>・スライド「バージョン管理の必要性」へ移行する。・図を指で示しながら説明する。</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>まず最初に、なぜGitHubが必要なのかをお話しします。皆さん、こういう経験はありませんか？ファイルを何度も修正していくうちに、『最終版.docx』『最終版_修正2.docx』『最終版_修正2_本当にこれが最終.docx』というファイルが増えていく、あの状態です。これは、ファイルの変更履歴を管理できていない状態です。特にプログラムのコードでは、この問題は致命的になります。なぜなら、新しい機能を追加したら前の機能が壊れた、どこを変えたかわからなくなった、昨日まで動いていたのに今日は動かない、といったことが頻繁に起きるからです。そのような問題を根本から解決するのが、バージョン管理という仕組みです。バージョン管理とは、ファイルの変更履歴を時系列で記録し、いつでも過去の状態に戻せる仕組みのことです。これがあれば、どんなに大胆な変更をしても、いつでも安全な状態に戻せます。</t>
         </is>
@@ -965,12 +968,12 @@
           <t>概念説明①</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>・スライド「バージョン管理の必要性」のまま。・ファイル名の山積みイラストを指して笑いを誘いつつ説明する。</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>バージョン管理の仕組みを使えば、ファイルは常に1つのままです。それでも、いつでも過去のどの時点の状態にも戻ることができます。例えば、3日前の状態に戻したい、1週間前のコードを参照したい、そういった操作が一瞬でできます。また、複数人で同じプロジェクトを進める場合、誰がいつ何を変えたかが一目でわかります。これはチームで開発する時に非常に重要です。このバージョン管理を実現するためのソフトウェアが、Gitです。そして、Gitで管理したファイルをインターネット上に保存・共有できるWebサービスが、GitHubです。この2つの違いを、次のスライドで丁寧に見ていきましょう。</t>
         </is>
@@ -997,12 +1000,12 @@
           <t>概念説明②</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>・スライド「GitとGitHubの違い」へ移行する。・図の左右を順番に指で示しながら説明する。</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>では、GitとGitHubの違いについてお話しします。まず、Gitとは何かです。Gitは、皆さんのPC上で動作するソフトウェアです。変更履歴の記録、過去の状態への復元、複数の作業ラインの管理、こういったことをPC上でできるようにするツールです。次に、GitHubとは何かです。GitHubは、Microsoft社が運営するWebサービスです。Gitで管理しているコードをインターネット上に保存・共有できます。わかりやすいたとえで言えば、GitはPC上の「日記帳」です。毎日の作業をこまめに書き留めておく道具です。GitHubはその日記帳を保管する「クラウドの金庫」です。金庫に入れておけば、PCが壊れても安心ですし、家族や友人と一緒に見ることもできます。もう少し技術的に言うと、ローカル環境、つまり皆さんのPCの中で変更を記録するのがGit、そのデータをリモート環境、つまりインターネット上に保存して管理するのがGitHubです。この2つは別物ですが、セットで使うことがほとんどです。この講座では、GitとGitHubを一緒に学んでいきます。</t>
         </is>
@@ -1029,12 +1032,12 @@
           <t>概念説明③</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>・スライド「リポジトリの概念図」へ移行する。・図のフォルダアイコンを指しながら説明する。</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>次に、GitHubを使うにあたって最初に覚えてほしい言葉が2つあります。1つめが、リポジトリです。リポジトリとは、プロジェクトに関するすべてのファイルと変更履歴をまとめて保管する場所のことです。一言で言えば、プロジェクト専用のフォルダです。ただし、普通のフォルダと違うのは、変更履歴もすべて記録されている点です。例えば、Webアプリを作るプロジェクトがあるとします。そのHTMLファイル、CSSファイル、JavaScriptファイル、画像ファイル、そしてそれらが誰によって、いつ、どのように変更されたか、そのすべての記録がリポジトリの中に入っています。リポジトリには2種類あります。1つはローカルリポジトリ、つまり皆さんのPC上にあるもの。もう1つはリモートリポジトリ、つまりGitHub上にあるものです。普段はローカルで作業して、定期的にGitHubのリモートリポジトリに反映する、という流れが基本です。この「反映する」操作のことを、プッシュと言います。覚えておいてください。</t>
         </is>
@@ -1061,12 +1064,12 @@
           <t>概念説明④</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>・スライド「コミットの概念図」へ移行する。・タイムライン上のポイントを順番に指で示す。</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>2つめの重要な言葉が、コミットです。コミットとは、ファイルの変更内容を記録する行為のことです。一言で言えば、セーブポイントです。ゲームで言えば、ここまで来たからセーブしておこう、という操作に相当します。コミットするたびに、その時点の状態がスナップショットとして保存されます。後でそのスナップショットに戻ることができます。コミットをする時には、コミットメッセージというメモをつけます。例えば、「ログイン機能を追加した」「バグを修正した」「デザインを変更した」といった内容です。このメモがあることで、後から見返したときに何をしたのかがすぐにわかります。チームで開発している場合は、誰がいつ何をしたかがメッセージから一目でわかります。コミットは、できるだけ小さな単位でこまめにする、というのが大切なルールです。大きな変更をまとめて1回でコミットするより、小さな変更を積み重ねてコミットする方が、後で問題が起きた時に対処しやすくなります。この考え方は、後で出てくる1タスク1コミットという概念とも深く関係しています。</t>
         </is>
@@ -1093,12 +1096,12 @@
           <t>実演①</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>・ブラウザ画面「GitHubアカウント作成」へ切り替える。・ブラウザの実際の操作を見せながら説明する。</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>では、実際にGitHubアカウントを作成してみましょう。ブラウザを開いて、github.comにアクセスします。右上に「Sign up」ボタンが見えますね。これをクリックします。最初にメールアドレスを入力します。自分のメールアドレスを入力してください。次にパスワードです。パスワードは、15文字以上のもの、または8文字以上で数字と小文字の英字を含むものが必要です。強固なパスワードを設定してください。次にユーザー名を設定します。ユーザー名は半角英数字とハイフンが使えます。これはGitHub上での皆さんの識別子になります。公開される情報なので、個人情報を含まないものを推奨します。入力が終わると、メールに認証コードが届きます。そのコードを画面に入力します。最後に料金プランを選択します。今回は無料の「Free」プランを選択してください。Freeプランでも、この講座で必要な操作はすべてできます。これでアカウントの作成は完了です。</t>
         </is>
@@ -1125,12 +1128,12 @@
           <t>実演②</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>・ブラウザ画面「リポジトリ画面案内」へ切り替える。・画面の各エリアを指で示しながら説明する。</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>アカウントが作成できたら、GitHubの画面を少し見ていきましょう。これがGitHubのリポジトリ画面です。最初は少し複雑に見えるかもしれませんが、よく使う部分だけ覚えれば大丈夫です。画面の上部には、リポジトリの名前が表示されています。その下に、Code・Issues・Pull requests・Actionsといったタブが並んでいます。最初によく使うのは、Codeタブです。ここにプロジェクトのすべてのファイルが表示されています。各ファイルの横には、最後にそのファイルを変更したコミットメッセージと、更新日時が表示されています。これで、誰がいつ何を変えたかが一目でわかります。画面右側には、About欄があります。リポジトリの説明やWebサイトのURLなどを設定できます。また、Public・Privateという設定があります。Publicにすると誰でも見られる公開状態、Privateにすると自分だけが見られる非公開状態になります。最初は私が利用するプロジェクトはPrivateで作ることをお勧めします。公開する準備ができたらPublicに変更できます。この画面の構成を覚えておくことで、次の動画で行うリポジトリの作成と操作がスムーズになります。</t>
         </is>
@@ -1157,12 +1160,12 @@
           <t>まとめ</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>・スライド「まとめ」へ切り替える。・スライドの要点を、講師が口頭でも繰り返す。</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>では、この動画をまとめます。今日学んだことを3点整理しましょう。1点め、バージョン管理とは、ファイルの変更履歴を時系列で記録し、いつでも過去の状態に戻せる仕組みです。『最終版の山』問題を根本から解決します。2点め、GitはPC上で動くバージョン管理ソフトウェア、GitHubはそのデータをクラウドに保存・共有するWebサービスです。Gitが日記帳で、GitHubがクラウドの金庫というたとえを覚えておいてください。3点め、リポジトリはプロジェクト専用のフォルダ、コミットはセーブポイントです。コミットはこまめに、コミットメッセージは何をしたかを明確に書くことが大切です。そして本日は実際にGitHubアカウントも作成しました。次の動画では、Claude Codeを使ってリポジトリを自動で作成する方法をお伝えします。いよいよAIとGitHubの組み合わせが始まります。楽しみにしていてください。</t>
         </is>
@@ -1189,12 +1192,12 @@
           <t>クロージング</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>・スライドは「まとめ」のまま。・講師が笑顔でカメラに向かって話す。</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>お疲れ様でした。GitHubの世界への第一歩、踏み出せましたね。最初はGitとGitHubの違いが混乱するかもしれませんが、使っていくうちに自然と身についていきます。配布資料の用語チートシートも活用しながら、焦らず進めてください。次の動画では、Claude Codeから直接GitHubリポジトリを作成する方法を実演します。AIがGitHub操作を代わりにやってくれる、あの便利さをぜひ体験してみてください。それでは、次の動画でお会いしましょう。</t>
         </is>
@@ -1788,12 +1791,12 @@
           <t>切替</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>・スライド「表紙」を表示する。・講師は笑顔で画面中央に向かって立つ。</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>前の動画でGitHubアカウントの作成ができましたね。お疲れ様でした。今日の動画では、さらに一歩進んで、Claude Codeを使ってGitHubリポジトリを自動で作成する方法をお伝えします。前回は「GitHubって何？」という概念の話でした。今回は「実際に手を動かして、AIにGitHub操作をやってもらう」という実践の話です。この動画を見終わった後には、ターミナルからコマンドひとつで、GitHubにリポジトリが作られてコードがアップロードされる体験ができます。では始めていきましょう。</t>
         </is>
@@ -1820,12 +1823,12 @@
           <t>導入</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>・スライド「gh CLIとは」へ移行する。・図を指で示しながら説明する。</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>まず最初に、gh CLIというツールについてお話しします。gh CLIとは、GitHub公式が提供するコマンドラインツールです。名前の「gh」は「GitHub」の略です。通常、GitHubを使う時はブラウザを開いてWebサイトにアクセスしますよね。でも、gh CLIを使えば、ブラウザを開かずにターミナルからGitHubを操作できます。リポジトリの作成、プルリクエストの管理、issueの確認、こういったことがすべてコマンドひとつでできます。ここで、少し混乱しやすいポイントをお伝えします。gitコマンドとghコマンドは別物です。gitコマンドは、ファイルの変更記録など、バージョン管理の操作をするものです。ghコマンドは、GitHubというサービスを操作するものです。例えば、「git commit」はローカルの変更を記録する操作、「gh repo create」はGitHub上にリポジトリを新規作成する操作です。この違いを意識しながら使っていくと、混乱が減ります。</t>
         </is>
@@ -1852,12 +1855,12 @@
           <t>概念説明</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>・スライド「操作フロー図」へ移行する。・フローを上から下へ順番に指で示す。</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>では、今日の動画で行う操作の全体フローを確認しておきましょう。ステップ1は、gh CLIのインストールです。まずターミナルでghコマンドが使えるようにします。ステップ2は、gh auth loginです。GitHubアカウントとgh CLIを連携させる認証作業です。最初に一度だけ行えばOKです。ステップ3は、プロジェクトフォルダの準備です。作業するフォルダを作り、Gitの初期化をします。ステップ4は、gh repo createコマンドでリポジトリを作成します。このコマンドひとつで、GitHub上にリポジトリが作られて、ローカルとの接続設定も完了します。ステップ5は、git add、git commit、git pushの3つの操作です。ファイルを変更記録に追加して、コミットして、GitHubにアップロードします。そして、このステップ3からステップ5を、Claude Codeに任せることができます。つまり、皆さんがやるのはステップ1と2のセットアップだけ。その後はClaude Codeに「GitHubにプッシュして」と伝えるだけでいいのです。これが今日の動画の最大のポイントです。</t>
         </is>
@@ -1884,12 +1887,12 @@
           <t>準備確認</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>・スライドは現状維持。・講師が事前準備の確認事項を列挙する。</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>実演に入る前に、準備の確認をしましょう。まず、前の動画でGitHubアカウントが作成済みであることを確認してください。次に、Macの場合は、Homebrewがインストールされている必要があります。Homebrewとは、MacにアプリをインストールするためのツールでPythonやNode.jsなど様々なツールのインストールにも使います。もしHomebrewが入っていない場合は、brew.shのサイトからインストールしておいてください。Windowsの場合は、wingetコマンドが使えます。こちらはWindowsに標準で入っていることがほとんどです。では、実演を始めます。ターミナルを開いてください。</t>
         </is>
@@ -1916,12 +1919,12 @@
           <t>実演①</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>・ターミナル画面「gh CLIインストールと認証」へ切り替える。・実際のコマンド入力を見せながら説明する。</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>まず、gh CLIをインストールします。Macの場合は「brew install gh」と入力してEnterを押します。少し待つとインストールが完了します。「gh --version」と入力して、バージョン番号が表示されればインストール成功です。次に、gh auth loginを実行します。「gh auth login」と入力してEnterを押します。最初に「Where do you use GitHub?」という質問が出ます。「GitHub.com」を選択してEnterを押します。次に「What is your preferred protocol for Git operations?」という質問が出ます。「HTTPS」を選択します。次に「Authenticate Git with your GitHub credentials?」という質問が出ます。「Yes」を選択します。次に「How would you like to authenticate GitHub CLI?」という質問が出ます。「Login with a web browser」を選択します。すると、「First copy your one-time code:」と表示されて、数字と文字の組み合わせコードが出てきます。このコードをコピーしておいてください。次に「Press Enter to open github.com in your browser...」と表示されたらEnterを押します。ブラウザが開いて、GitHubのページが表示されます。コードを入力する欄に先ほどコピーしたコードを貼り付けて、Authorizeボタンを押します。ブラウザで認証が完了したら、ターミナルに戻ると「Logged in as ユーザー名」と表示されているはずです。これで認証完了です。</t>
         </is>
@@ -1948,12 +1951,12 @@
           <t>実演②</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>・ターミナル画面「リポジトリ作成とpush」へ切り替える。・操作を一つずつ見せながら説明する。</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>では次に、リポジトリを作成してpushするまでを実演します。まず、プロジェクト用のフォルダを作ります。「mkdir my-first-repo」と入力してEnterを押します。「cd my-first-repo」でフォルダの中に移動します。次に、「git init」でGitの初期化をします。これで、このフォルダでGitが使えるようになりました。続いて、gh repo createコマンドでGitHub上にリポジトリを作成します。「gh repo create my-first-repo --public --source=. --remote=origin」と入力します。少し説明すると、「--public」は公開リポジトリにするオプション、「--source=.」は現在のフォルダをソースにするオプション、「--remote=origin」はリモート名をoriginにするオプションです。このコマンドひとつで、GitHub上にリポジトリが作られて、ローカルとの接続設定まで完了します。次に、テスト用にファイルを1つ作ります。「echo Hello GitHub &gt; README.md」と入力します。それから3つのコマンドを実行します。「git add README.md」でファイルを変更記録に追加、「git commit -m 最初のコミット」で変更を記録、「git push -u origin main」でGitHubにアップロードです。プッシュが完了したら、ブラウザでGitHubを開いてみてください。作成したリポジトリにファイルがアップロードされているはずです。この一連の操作が、Claude Codeへの指示ひとつで自動化できます。</t>
         </is>
@@ -1980,12 +1983,12 @@
           <t>Claude Code活用</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>・スライドへ戻す。・Claude Codeとの連携部分を強調して説明する。</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>今、皆さんに手動でコマンドを実行してもらいましたが、これをClaude Codeに任せることができます。Claude Codeのターミナルで、「このプロジェクトをGitHubにプッシュしてください」と日本語で伝えるだけです。するとClaude Codeが、git addからgit commitそしてgit pushまでを自動で実行してくれます。でも、なぜ今日は手動でやってもらったかというと、仕組みを知ったうえで自動化に任せることが大切だからです。何をしているのかわからないまま自動化に頼ると、問題が起きた時に対処できません。仕組みを理解してから自動化することで、トラブル時の対応力も上がります。これが、この動画で手動操作を見せた理由です。</t>
         </is>
@@ -2012,12 +2015,12 @@
           <t>まとめ</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>・スライド「まとめ」へ切り替える。・スライドの要点を、講師が口頭でも繰り返す。</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>では、この動画をまとめます。今日学んだことを整理しましょう。gh CLIとは、GitHub公式のコマンドラインツールです。ブラウザを開かずにターミナルからGitHubを操作できます。gitコマンドはバージョン管理、ghコマンドはGitHubサービス操作、この2つは別物です。gh auth loginで認証を行えば、gh repo createコマンドひとつでGitHub上にリポジトリを作成できます。そして、git add、git commit、git pushの3ステップでコードをGitHubにアップロードできます。最も大切なのは、この一連の流れをClaude Codeに任せることができるという点です。仕組みを理解したうえでAIに委ねる、これがこの講座のスタンスです。次の動画では、ファイルの参照機能である@インポートと、権限管理について学びます。Claude Codeをより安全に、より効率的に使うための設定です。</t>
         </is>
@@ -2044,12 +2047,12 @@
           <t>クロージング</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>・スライドは「まとめ」のまま。・講師が笑顔でカメラに向かって話す。</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>お疲れ様でした。リポジトリの作成とプッシュ、うまくできましたか？最初はコマンドが多くて大変に感じるかもしれませんが、これも慣れていくものです。配布資料のghコマンドチートシートを手元に置いておくと、いざという時に参照できて便利です。次の動画もお楽しみに。それでは、次の動画でお会いしましょう。</t>
         </is>
@@ -2653,12 +2656,12 @@
           <t>切替</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>・スライド「表紙」を表示する。・講師は笑顔で画面中央に向かって立つ。</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>皆さん、こんにちは。今日の動画では、Claude Codeをより賢く、より安全に使うための2つの機能を学びます。1つめが@インポート、つまりファイルの参照機能です。2つめがパーミッション管理、つまり権限の設定です。この2つを理解することで、Claude Codeに「どのファイルを読んでほしいか」「どんな操作を許可するか」を細かくコントロールできるようになります。これはただ便利なだけでなく、安全にAIを使うためにも非常に重要な知識です。ぜひ最後まで見ていただければと思います。</t>
         </is>
@@ -2685,12 +2688,12 @@
           <t>導入</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>・スライド「@インポートの仕組み」へ移行する。・図を指で示しながら説明する。</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>まず、@インポートの仕組みをお話しします。Claude Codeにプロンプトを送る時、プロンプトの中に「@ファイルパス」と書くことができます。こうすると、そのファイルの内容がClaude Codeのコンテキスト、つまり「今回の作業で参照できる情報」に自動的に読み込まれます。例えば、「@docs/requirements.md を参照して、ログイン機能を実装してください」と書くと、Claude Codeはrequirements.mdの内容を読んだうえで、その仕様に合ったログイン機能を実装してくれます。ファイルを参照しながら指示を出せるのは、非常に強力な機能です。人間でいえば、「この設計書を見ながらコードを書いてください」という指示に相当します。設計書の内容を毎回プロンプトに貼り付ける必要がなく、@ファイルパスと書くだけで済みます。</t>
         </is>
@@ -2717,12 +2720,12 @@
           <t>概念説明</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>・スライド「@インポートの仕組み」のまま。・活用パターンを箇条書きで示しながら説明する。</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>@インポートの活用パターンについてお話しします。まず、既存コードを参考に新しいコードを書く場合です。例えば、既存のボタンコンポーネントのスタイルに合わせた新しいコンポーネントを作りたい時、「@src/components/Button.jsx を参考に、同じスタイルのInputコンポーネントを作成してください」と指示できます。これで、スタイルや命名規則を自動的に統一した出力が得られます。次に、エラーログを渡して修正を依頼する場合です。「@error.log このエラーを修正してください」と書くと、エラーの内容をClaude Codeが正確に把握して修正提案をしてくれます。また、フォルダをまるごと指定することも可能です。「@src/utils/ このフォルダ全体を参照して、統一感のあるコードを追加してください」という使い方です。そして、後で詳しく説明しますが、設計書を@インポートで参照させながら実装を進めるスペック駆動開発への応用が最も強力です。</t>
         </is>
@@ -2749,12 +2752,12 @@
           <t>実演①</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>・ターミナル画面「@インポート実演」へ切り替える。・実際の@インポートの使い方を見せる。</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>では、実際に@インポートを使ってみましょう。まず、サンプルのプロジェクトフォルダを開いてください。ここに、docs/requirements.mdというファイルがあります。このファイルの中には、簡単な要件定義が書かれています。Claude Codeを起動して、プロンプトに「@docs/requirements.md を参照して、このプロジェクトの概要を日本語で教えてください」と入力してみます。するとClaude Codeが、requirements.mdの内容を読み込んで、その内容に基づいた回答を返してくれます。ファイルパスは、プロジェクトフォルダからの相対パスで書いてください。つまり、「@docs/requirements.md」と書けば、現在のフォルダの中のdocsフォルダの中のrequirements.mdというファイルを参照します。URLも使えます。例えば「@https://example.com/api-docs」と書けば、そのWebページの内容を読み込んで参照できます。公式ドキュメントを参照させながらコードを書かせる時に便利です。この@インポートの機能は、スペック駆動開発の核心的な機能です。設計書を参照させながら実装を進めることで、AIが全体像を理解した状態でコードを書いてくれます。</t>
         </is>
@@ -2781,12 +2784,12 @@
           <t>概念説明②</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>・スライド「パーミッション解説」へ切り替える。・図の各権限レベルを指しながら説明する。</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>次に、パーミッション管理についてお話しします。パーミッションとは、Claude Codeに「何をしてよくて、何をしてはいけないか」を設定する仕組みです。デフォルトでは、Claude Codeは操作ごとに確認を求めてきます。「このファイルを書き換えてよいですか？」「このコマンドを実行してよいですか？」といった確認です。これは安全ですが、毎回確認が出てくるのが少し面倒なこともあります。パーミッション設定を使えば、「このフォルダの中のファイルは読み書き自由」「このコマンドは事前許可済みで確認不要」といった設定ができます。パーミッションには段階があります。最も制限の少ない「読み取りのみ許可」、次に「書き込みも許可」、さらに「シェルコマンドの実行も許可」という段階があります。設定は、プロジェクトの.claude/settings.jsonというファイルで行います。</t>
         </is>
@@ -2813,12 +2816,12 @@
           <t>実演②</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>・ターミナル画面「パーミッション設定実演」へ切り替える。・設定ファイルの編集を実際に見せる。</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>では、パーミッション設定の実演をします。プロジェクトフォルダの中に.claude/settings.jsonというファイルを作成します。このファイルに許可するツールと拒否するツールを記述します。例えば、ファイルの読み取りとシェルコマンドの実行を許可する場合はallowツールにReadとBashを追加します。逆に、特定の操作を禁止したい場合はdenyに追加します。これで、毎回確認なしに許可した操作を実行してもらえるようになります。実際にどんな設定をするかは、プロジェクトや作業の内容によって変わります。最初は慎重な設定から始めて、慣れてきたら少しずつ緩めるというアプローチが安全です。大切なポイントは「信頼するけど検証する」という姿勢です。AIの変更提案は、適用前に一度確認する習慣をつけましょう。</t>
         </is>
@@ -2845,12 +2848,12 @@
           <t>実演③</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>・スライド「.claudeignoreの使い方」へ切り替える。・設定例を見せながら説明する。</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>パーミッション管理のもうひとつの重要な機能が、.claudeignoreです。.claudeignoreとは、Claude Codeに読ませたくないファイルやフォルダを指定する設定ファイルです。これは、Gitで使う.gitignoreと同じ仕組みです。なぜ必要かというと、すべてのファイルをClaude Codeに読ませる必要はないからです。特に、セキュリティ上の理由で読ませたくないファイルがあります。最も重要なのが.envファイルです。.envファイルには、APIキーやパスワードといった秘密の情報が入っています。これをClaude Codeに読まれてしまうと、情報漏洩のリスクがあります。また、node_modulesフォルダには大量のライブラリファイルが入っています。これを全部読もうとすると、時間がかかるうえにClaude Codeのコンテキストを無駄に使ってしまいます。.claudeignoreの書き方は.gitignoreと同じです。プロジェクトのルートフォルダに.claudeignoreというファイルを作り、除外したいファイルやフォルダをひとつずつ書いていきます。基本的なテンプレートとして、.envファイルと.env.localファイルとnode_modulesフォルダとdistフォルダを除外設定しておくことをお勧めします。新しいプロジェクトを始める時には、まず最初にこの.claudeignoreを作成する習慣をつけてください。</t>
         </is>
@@ -2877,12 +2880,12 @@
           <t>まとめ</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>・スライド「まとめ」へ切り替える。・スライドの要点を、講師が口頭でも繰り返す。</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>では、この動画をまとめます。今日学んだことを整理しましょう。@インポートとは、プロンプト内に「@ファイルパス」と書くことで、そのファイルの内容をClaude Codeのコンテキストに読み込む機能です。設計書を参照させながら実装を指示するスペック駆動開発の核心機能です。パーミッション管理とは、Claude Codeに「何をしてよくて何をしてはいけないか」を設定する仕組みです。.claude/settings.jsonで許可・拒否するツールを明示的に指定できます。.claudeignoreとは、Claude Codeに読ませたくないファイルを除外する設定ファイルです。APIキーなどの秘密情報を含む.envファイルは必ず除外しましょう。この3つのセットアップを最初に行うことで、安全で効率的な開発環境が整います。次の動画では、いよいよスペック駆動開発の考え方について、詳しくお話しします。</t>
         </is>
@@ -2909,12 +2912,12 @@
           <t>クロージング</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>・スライドは「まとめ」のまま。・講師が笑顔でカメラに向かって話す。</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>お疲れ様でした。@インポートとパーミッション管理、理解できましたか？最初は設定することが多くて大変に感じるかもしれませんが、これらは一度設定してしまえばプロジェクトを通して使えます。配布資料のパーミッション設定早見表も参考にしながら、自分のプロジェクトに合った設定を見つけていってください。次の動画では、スペック駆動開発という考え方について詳しく学びます。それでは、次の動画でお会いしましょう。</t>
         </is>
@@ -3491,12 +3494,12 @@
           <t>切替</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>・スライド「表紙」を表示する。・講師は少し真剣な表情で画面中央に向かって立つ。</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>皆さん、こんにちは。今日の動画は、この講座の中でも特に重要なテーマです。タイトルにある「スペック駆動開発」という言葉、初めて聞く方も多いと思います。この考え方を知っているかどうかで、プロジェクトの成功率が大きく変わります。実は、Claude Codeを最初に触った多くの方が「雑に指示を出しても動くものができる！」という体験をします。でも、それだけでは必ずどこかで壁に当たります。今日は、その壁がどこでなぜ起きるのか、そしてどうすれば乗り越えられるのかをお話しします。</t>
         </is>
@@ -3523,12 +3526,12 @@
           <t>導入</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>・スライド「Vibe Codingの図解」へ移行する。・図を指で示しながら説明する。</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>まず、Vibe Codingという言葉を説明します。Vibe Codingとは、細かい仕様を決めずに「雰囲気」でAIに開発を進めさせるスタイルのことです。英語のVibe、つまり「雰囲気」や「感覚」から来た言葉です。具体的には、「なんかTodoアプリを作って」「ログインできるようにして」「ちょっとデザインをかっこよくして」というような、ざっくりとした指示を次々と出していくやり方です。このアプローチは、最初のうちは非常に快適です。思ったよりすぐに動くものができるので、AIって本当に便利だなと感じます。実際、プロトタイプや簡単なツールを作る場合は、これで十分なことも多いです。問題は、このアプローチで本格的なプロジェクトを進めようとした時です。</t>
         </is>
@@ -3555,12 +3558,12 @@
           <t>問題提起</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>・スライド「Vibe Codingの図解」のまま。・AIの「その場のベスト」という概念を強調する。</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Vibe Codingがうまくいかなくなるのは、機能が増えてきた時です。AIは、毎回の指示に対してその場のベストを尽くします。ですが、AIは全体像を把握していません。例えばこういうことが起きます。最初に「ユーザー登録機能を作って」と言いました。AIがコードを書きます。次に「商品一覧ページを作って」と言いました。AIがコードを書きます。次に「カートに追加する機能を作って」と言いました。AIがコードを書きます。ここまではよかったのですが、次に「ユーザーごとのカート履歴を表示して」と言ったら、最初に作ったユーザー登録の仕組みとカートの仕組みが整合していなくて、うまく繋がらない、ということが起きます。これが「もぐら叩き」状態です。ひとつ直すと別のところが壊れる。また直すとまた別のところが壊れる。この繰り返しになってしまいます。なぜこうなるかというと、設計図なしに家を建てているようなものだからです。大工さんがどれだけ腕が良くても、設計図がなければ整合性のある家は建てられません。</t>
         </is>
@@ -3587,12 +3590,12 @@
           <t>破綻の具体例</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>・スライド「破綻の具体例」へ移行する。・問題のある状況を具体的に描写する。</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>では、実際にどういう状況で破綻が起きるか、もう少し具体的にお話しします。例えば、簡単なEコマースサイトを作るとします。最初の段階で「商品を表示するページを作って」と指示しました。AIはシンプルな静的HTMLのページを作りました。次に「ユーザーがログインできるようにして」と指示しました。AIはログイン機能を追加しました。次に「ユーザーごとに購入履歴を見られるようにして」と指示しました。ここで問題が起きます。最初に作ったページは静的なHTMLなので、ユーザー別のデータを扱う設計になっていません。ログイン機能もユーザーデータをどこに保存するかをその場で決めたため、購入履歴との整合性がとれていません。この状態を修正しようとすると、最初から作り直したほうが早いというケースも出てきます。これが機能が5つ10と増えた時の「もぐら叩き」状態です。AIのせいではありません。設計なしに進めたことが原因です。この問題を根本から解決するのが、スペック駆動開発という考え方です。</t>
         </is>
@@ -3619,12 +3622,12 @@
           <t>スペック駆動開発の説明</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>・スライド「スペック駆動開発の図解」へ移行する。・4ステップを上から順に指で示す。</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>スペック駆動開発とは何かを説明します。スペックとは仕様、つまり「作るものの条件を文書化したもの」のことです。スペック駆動開発とは、コードを書く前に仕様書を先に作り、その仕様書に従って段階的に実装していく開発手法です。流れは4ステップです。ステップ1が要件定義書の作成です。「何を作るか」「誰が使うか」「どんな機能が必要か」を文書化します。ステップ2が設計書の作成です。「どう作るか」「どんな技術を使うか」「データをどう構造化するか」を文書化します。ステップ3がタスクリストの作成です。設計書の内容を、実装できる単位に分解したチェックリストを作ります。ステップ4がタスクごとの実装です。タスクリストの上から順番に、ひとつずつ実装していきます。この4ステップで重要なのは、コードを書く前に最初の3ステップが完了していることです。仕様書があることで、AIは全体像を理解した状態でコードを書けます。その結果、整合性のある出力が得られ、「もぐら叩き」状態を防げます。そしてこの仕様書は、Claude Codeと一緒に壁打ちしながら作れます。難しく考える必要はありません。</t>
         </is>
@@ -3651,12 +3654,12 @@
           <t>docs構成の説明</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>・スライド「docs構成の例」へ移行する。・フォルダ構成をファイルごとに指して説明する。</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>スペック駆動開発では、仕様書をdocsフォルダにまとめて管理します。docsフォルダには3つのファイルを置きます。1つめがdocs/requirements.mdです。要件定義書です。「何を作るか」「誰が使うか」「必要な機能は何か」が書かれています。2つめがdocs/design.mdです。設計書です。「どんな技術を使うか」「画面遷移はどうなっているか」「データをどう構造化するか」が書かれています。3つめがdocs/tasks.mdです。タスクリストです。設計書の内容を作業単位に分解したチェックリストです。この3ファイルがプロジェクトの地図になります。実装する時は、@インポートでこれらのファイルをClaude Codeに参照させながら指示を出します。前の動画で学んだ@インポートが、ここで活きてきます。また、このdocsフォルダはGitHubリポジトリにコミットして管理します。チームで開発している場合は、誰でも最新の仕様を確認できます。仕様書は「固定されたもの」ではなく、開発と一緒に成長していくものです。実装が進むにつれて、仕様書も更新されていきます。</t>
         </is>
@@ -3683,12 +3686,12 @@
           <t>比較まとめ</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>・スライド「比較まとめ」へ移行する。・表の各行を指して比較を説明する。</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>では、Vibe CodingとSpecs駆動開発の違いを整理しましょう。Vibe Codingは、仕様書なし、指示は雰囲気ベース、問題が起きた時に対処するリアクティブなアプローチです。小規模なプロジェクトやプロトタイプには向いています。スペック駆動開発は、仕様書あり、指示は仕様書ベース、問題を未然に防ぐプロアクティブなアプローチです。本格的なプロジェクトに向いています。どちらが優れているかではなく、場面に応じた使い分けが大切です。アイデアの検証や小さなツールならVibe Codingで十分です。本格的なプロジェクトならスペック駆動がおすすめです。この講座の残りの動画では、スペック駆動開発の具体的なやり方を実演形式でお伝えしていきます。</t>
         </is>
@@ -3715,12 +3718,12 @@
           <t>まとめ</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>・スライド「まとめ」へ切り替える。・スライドの要点を、講師が口頭でも繰り返す。</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>では、この動画をまとめます。Vibe Codingとは、細かい仕様を決めずに雰囲気でAIに開発を進めさせるスタイルです。小規模プロジェクトには向きますが、機能が増えると「もぐら叩き」状態に陥りやすいです。その根本的な原因は、AIが全体像を把握していない状態でコードを書いているからです。スペック駆動開発とは、コードを書く前に要件定義書・設計書・タスクリストを作り、それを地図として開発を進める手法です。docsフォルダに3ファイルを置き、@インポートで参照させながら実装することで、整合性のある出力が得られます。Vibe CodingとSpecs駆動開発の使い分けが、賢いAI活用の鍵です。次の動画では、実際にClaude Codeと壁打ちして要件定義書を作る過程を実演します。</t>
         </is>
@@ -3747,12 +3750,12 @@
           <t>クロージング</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>・スライドは「まとめ」のまま。・講師が明るい表情でカメラに向かって話す。</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>お疲れ様でした。スペック駆動開発という考え方、いかがでしたか？最初は「そんな手間をかける必要があるの？」と思われる方もいるかもしれません。でも、仕様書を作る時間は、後の「もぐら叩き」に費やす時間と比べると、はるかに短いです。最初に少し手間をかけることで、後が楽になる。これがスペック駆動開発の魅力です。次の動画では、Claude Codeとの壁打ちを実演します。要件定義書を一緒に作るプロセスを見ていただきます。楽しみにしていてください。それでは、次の動画でお会いしましょう。</t>
         </is>
@@ -4373,12 +4376,12 @@
           <t>切替</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>・スライド「表紙」を表示する。・講師は笑顔で画面中央に向かって立つ。</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>皆さん、こんにちは。前の動画ではスペック駆動開発という考え方をお伝えしました。今日はその最初のステップである要件定義について、実際にClaude Codeと壁打ちしながら要件定義書を作るプロセスを実演します。「何を作りたいかは頭の中にあるんだけど、うまく言葉にできない」という経験はありませんか？この動画を見終わった後には、そのもやっとしたアイデアをAIとの対話を通じて明確な要件定義書に変換できるようになっているはずです。では始めましょう。</t>
         </is>
@@ -4405,12 +4408,12 @@
           <t>導入</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>・スライド「要件定義とは」へ移行する。・図を指で示しながら説明する。</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>まず、要件定義とは何かをお話しします。要件定義とは、「作るものの条件を決める」作業のことです。具体的には、誰が使うのか、どんな機能が必要か、どんな場面で使われるか、逆にできなくてよいことは何か、こういったことを明文化します。なぜこれが重要かというと、頭の中の曖昧なイメージと実際に動くものの間には、大きなギャップが生まれやすいからです。要件定義とは、そのギャップを埋める作業です。「誰が読んでも同じものを想像できる文章にする」というのが目標です。この丁寧さが後の開発品質を大きく左右します。そして、この要件定義をClaude Codeと一緒に作れるのが、スペック駆動開発の強みです。</t>
         </is>
@@ -4437,12 +4440,12 @@
           <t>概念説明</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>・スライド「要件定義とは」のまま。・詳しい説明を続ける。</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>要件定義で答えるべき4つの問いがあります。1つめは「誰が使うか」です。ターゲットユーザーは誰ですか？初心者向けですか？専門家向けですか？ユーザー数はどれくらいを想定していますか？2つめは「何ができるか」です。必要な機能のリストです。ユーザーができることを「誰が、何をできる」という形式で書き出します。3つめは「どんな場面で使われるか」です。スマートフォンからも使いますか？特定のOSに限定しますか？オフラインでも使えるようにしますか？4つめは「できなくてよいことは何か」です。これを明確にすることで、スコープが広がりすぎるのを防ぎます。最初のバージョンで作らないものを決めることも、要件定義の重要な仕事です。この4つを意識しながら壁打ちを進めていきます。</t>
         </is>
@@ -4469,12 +4472,12 @@
           <t>壁打ちの進め方</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>・スライド「壁打ちの進め方」へ移行する。・3ステップを上から順に指で示す。</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>では、AIとの壁打ちの進め方をお話しします。3ステップです。ステップ1は、ざっくりした想いを伝えることです。完璧に整理されていなくて大丈夫です。「こんなものを作りたい」という思いを、そのままClaude Codeに伝えます。ステップ2は、AIからの深掘り質問に答えることです。Claude Codeが「対象ユーザーは？」「データはどこに保存しますか？」「通知機能は必要ですか？」という質問をしてきます。この質問に答えていくことで、自分でも気づいていなかった論点が浮かび上がります。5回から10回の対話で、具体的な要件が出揃います。ステップ3は、整理された要件を確認して修正することです。Claude Codeが要件を整理してくれたら、見落としや誤解がないか確認して、必要なら修正します。このプロセスが完了したら、要件定義書としてファイルに保存します。では実際に実演してみましょう。</t>
         </is>
@@ -4501,12 +4504,12 @@
           <t>実演</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>・ターミナル画面「Claude Codeとの壁打ち実演」へ切り替える。・対話の様子を実際に見せながら解説する。</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>では実際に壁打ちを始めます。今回は例として、「社内向けの備品管理アプリ」を作るという想定で進めます。Claude Codeを起動して、最初のメッセージを送ります。「社内の備品を管理するWebアプリを作りたいです。要件定義を一緒に考えてください。備品の貸し出し管理と在庫管理ができるものを想定しています」と入力します。するとClaude Codeが、いくつかの質問を返してきます。「ユーザーは何人くらいを想定していますか？」「備品の種類はどれくらいありますか？」「貸し出しの申請は誰が承認しますか？」こういった質問です。一つひとつ答えていきます。「ユーザーは社員全員で約50人です。」「備品はパソコン、モニター、カメラなど約100種類です。」「貸し出しは申請不要、先着順で使えるようにしたいです。」このやり取りを続けていくと、どんどん要件が具体化していきます。「データはクラウドに保存しますか？」「スマートフォンからも使えるようにしますか？」「在庫切れになった場合の通知機能は必要ですか？」さらに答えていきます。「クラウドに保存してほしいです。」「スマートフォン対応もほしいです。」「在庫切れ通知は最初のバージョンではなくていいです。」これが対象外機能の明確化です。5回から10回のやり取りで、かなり具体的な要件が出揃ってきました。最後に「ここまでの対話をもとにdocs/requirements.mdとして要件定義書を作成してください」と指示します。するとClaude Codeが、プロジェクト概要・ターゲットユーザー・機能要件・非機能要件・対象外・将来的な拡張候補という構成で要件定義書を生成してくれます。</t>
         </is>
@@ -4533,12 +4536,12 @@
           <t>要件定義書確認</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>・エディタ画面「生成された要件定義書の確認」へ切り替える。・生成されたファイルの構成を案内する。</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>生成されたrequirements.mdを確認してみましょう。エディタで開くと、マークダウン形式できれいに整理された要件定義書が出来上がっています。先ほどの対話の内容が、整理されてまとまっています。プロジェクト概要のセクションには、何を作るかとなぜ作るかが書かれています。ターゲットユーザーのセクションには、誰がどんな課題を抱えているかが書かれています。機能要件のセクションには、誰が何をできるかという形式で機能が列挙されています。非機能要件のセクションには、性能やセキュリティについての要件が書かれています。対象外のセクションには、今回作らないものが明記されています。将来的な拡張候補のセクションには、次のバージョンで追加できそうなアイデアが挙げられています。この要件定義書が、次のステップである設計書・タスクリスト作成の土台になります。</t>
         </is>
@@ -4565,12 +4568,12 @@
           <t>テンプレート説明</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>・スライド「要件定義テンプレート」へ切り替える。・各セクションを指して説明する。</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>要件定義書のテンプレートについて説明します。配布資料として皆さんにもお渡ししますが、このテンプレートの構成を理解しておくことが大切です。テンプレートの6つのセクションを説明します。1つめはプロジェクト概要です。何を作るか、なぜ作るかを1から2文でまとめます。2つめはターゲットユーザーです。誰が使うか、そのユーザーはどんな課題を抱えているかを書きます。3つめは機能要件です。「誰が、何をできる」という形式で機能を列挙します。例えば「管理者が、備品の一覧を確認できる」「社員が、備品の貸し出し申請ができる」という形式です。4つめは非機能要件です。性能・セキュリティ・対応ブラウザ・レスポンシブ対応などを記述します。5つめは対象外です。今回作らないものを明記します。スコープが広がりすぎるのを防ぐ重要なセクションです。6つめは将来的な拡張候補です。今回は作らないが次回以降に追加できそうな機能を書き留めておきます。このテンプレートを使って、自分のプロジェクトの要件定義書を作ってみてください。Claude Codeとの壁打ちを通じて、このテンプレートを埋めていくことができます。</t>
         </is>
@@ -4597,12 +4600,12 @@
           <t>まとめ</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>・スライド「まとめ」へ切り替える。・スライドの要点を、講師が口頭でも繰り返す。</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>では、この動画をまとめます。要件定義とは、「作るものの条件を誰が読んでも同じものを想像できる文章にする」作業です。Claude Codeとの壁打ちは3ステップです。ざっくりした想いを伝える、深掘り質問に答える、整理された要件を確認・修正する。5回から10回の対話で具体的な要件が出揃います。要件定義書は6つのセクション構成です。プロジェクト概要・ターゲットユーザー・機能要件・非機能要件・対象外・将来的な拡張候補です。「ここまでの会話をもとにdocs/requirements.mdを作成してください」という指示ひとつで、整理された要件定義書が生成されます。次の動画では、この要件定義書をもとに設計書とタスクリストを自動生成します。</t>
         </is>
@@ -4629,12 +4632,12 @@
           <t>クロージング</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>・スライドは「まとめ」のまま。・講師が笑顔でカメラに向かって話す。</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>お疲れ様でした。Claude Codeとの壁打ちで要件定義書を作るプロセス、いかがでしたか？最初は「こんなざっくりした話で大丈夫？」と感じるかもしれませんが、AIが上手く引き出してくれます。ぜひ自分のアイデアで試してみてください。配布資料のテンプレートも活用してください。次の動画では、この要件定義書から設計書とタスクリストを自動生成します。スペック駆動開発の核心部分です。楽しみにしていてください。それでは、次の動画でお会いしましょう。</t>
         </is>
@@ -5255,12 +5258,12 @@
           <t>切替</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>・スライド「表紙」を表示する。・講師は笑顔で画面中央に向かって立つ。</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>皆さん、こんにちは。前の動画では、Claude Codeとの壁打ちを通じて要件定義書を作りました。今日はその続きです。要件定義書から設計書とタスクリストを自動生成して、実際に実装をスタートするところまでお見せします。この動画を見終わった後には、要件定義書さえあれば、あとはClaude Codeが設計書・タスクリストを作ってくれて、その指示通りに実装を進められる、というワークフローが身についているはずです。スペック駆動開発の核心部分です。ぜひ最後まで見ていってください。</t>
         </is>
@@ -5287,12 +5290,12 @@
           <t>導入</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>・スライド「設計書の役割」へ移行する。・図を指で示しながら説明する。</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>まず、設計書とは何かをお話しします。設計書と要件定義書、似ているようで役割が違います。要件定義書は「何を作るか」を定義するものです。「誰が使うか」「どんな機能があるか」が書かれています。設計書は「どう作るか」を定義するものです。「どんな技術を使うか」「どうデータを構造化するか」「画面遷移はどうなっているか」が書かれています。家を建てる例えで言うと、要件定義書が「4LDKの家で、庭付きで、駐車場も欲しい」という要望書だとすれば、設計書は「基礎はコンクリート造、壁は木造、配線はここを通って、配管はここを通って」という建築設計図です。この設計書があることで、AIは整合性のあるコードを書けます。</t>
         </is>
@@ -5319,12 +5322,12 @@
           <t>設計書の内容説明</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>・スライド「設計書の役割」のまま。・設計書の5項目を順番に説明する。</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>設計書に含める主な項目は5つです。1つめは技術スタックの選定です。フロントエンドはReactかVueか、バックエンドはNode.jsかPythonか、データベースはPostgreSQLかMongoDBか、こういった技術の選択を記述します。2つめはディレクトリ構成です。プロジェクトのフォルダ構成を記述します。どのフォルダにどのファイルを置くかを決めておくことで、実装がバラバラにならなくなります。3つめは画面遷移図です。ユーザーがどの画面からどの画面に移動するかを図で示します。4つめはデータモデルの定義です。データベースにどういうデータを保存するか、どういう構造で保存するかを記述します。5つめはAPI設計です。フロントエンドとバックエンドの間でどういうデータをやり取りするかを定義します。これら5つが設計書の基本構成です。全部完璧に書く必要はありません。プロジェクトの規模に応じて、必要な項目を選んで書いていきます。</t>
         </is>
@@ -5351,12 +5354,12 @@
           <t>実演①</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>・ターミナル画面「設計書の自動生成」へ切り替える。・設計書の生成過程を実際に見せる。</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>では、設計書の自動生成を実演します。前の動画で作成したdocs/requirements.mdがあります。このファイルを@インポートでClaude Codeに参照させて、設計書を作成させます。Claude Codeに「@docs/requirements.md の要件定義書を読んで、技術設計書をdocs/design.mdとして作成してください」と指示します。するとClaude Codeが、要件定義書の内容を理解したうえで設計書を自動生成します。出力されたdesign.mdを確認してみましょう。技術スタックの選定として、フロントエンドはReact、バックエンドはNode.js、データベースはPostgreSQLが選ばれています。次にディレクトリ構成が示されています。srcフォルダの中にcomponents・pages・apiフォルダが配置された構成です。さらに画面遷移図がmermaid記法で書かれています。データモデルには、ユーザーテーブルと備品テーブルと貸し出し記録テーブルが定義されています。これが自動で生成されました。もし技術スタックを変更したい場合は、「フロントエンドをVueに変更してください」と追加指示するだけです。設計書は固定ではなく、チームの事情や好みに合わせて調整できます。</t>
         </is>
@@ -5383,12 +5386,12 @@
           <t>タスク分解の説明</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>・スライド「タスク分解の考え方」へ移行する。・粒度の考え方を図で示す。</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>次に、タスクリストについてお話しします。タスクリストとは、設計書の内容を「ひとつずつ実装できる単位」に分けたチェックリストのことです。タスクの粒度、つまり大きさが重要です。「Webアプリを作る」というのはタスクが大きすぎます。逆に「変数を1つ追加する」は小さすぎます。ちょうどいい粒度は、「1タスクをClaude Codeに指示したら10分から30分で完了する」規模です。具体的には、「ユーザーモデルを定義する」「ログイン画面のHTMLを作成する」「ログインAPIエンドポイントを作成する」「ログイン画面とAPIを繋ぐ」という単位です。そして、1タスク1コミットというルールが重要です。タスクが完了したらコミット、また次のタスクが完了したらコミット、という習慣です。このルールにより、問題が発生した時に直前の安定状態にすぐ戻れる安心感が生まれます。</t>
         </is>
@@ -5415,12 +5418,12 @@
           <t>実演②</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>・ターミナル画面「タスクリスト生成」へ切り替える。・タスクリストの生成過程を実際に見せる。</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>では、タスクリストの生成を実演します。設計書が完成したので、今度はタスクリストを作ります。Claude Codeに「@docs/requirements.md と @docs/design.md を読んで、実装タスクをdocs/tasks.mdとして作成してください。1タスクは30分以内で完了できる粒度にしてください」と指示します。するとClaude Codeが、設計書の内容を実装タスクに分解したチェックリストを作成してくれます。生成されたtasks.mdを確認してみましょう。プロジェクト初期設定、データベース設計、バックエンドAPI実装、フロントエンド実装、という大きな工程に分かれて、それぞれの工程の下に具体的なタスクがチェックボックス形式で並んでいます。例えばデータベース設計の下には、ユーザーテーブルの作成、備品テーブルの作成、貸し出し記録テーブルの作成、というタスクが並んでいます。このリストが実装のロードマップになります。上から順番に実装していくことで、整合性のあるプロジェクトが完成します。</t>
         </is>
@@ -5447,12 +5450,12 @@
           <t>実演③</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>・ターミナル画面「タスク実装とコミット」へ切り替える。・1タスクの実装からコミットまでを見せる。</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>では、実際に1つのタスクを実装する様子をお見せします。タスクリストの最初のタスクを選びます。「プロジェクトの初期設定」です。Claude Codeに「@docs/design.md を参照して、タスクリストの最初のタスク『プロジェクト初期設定』を実装してください」と指示します。するとClaude Codeが、Node.jsプロジェクトの初期化、必要なライブラリのインストール、基本的なディレクトリ構造の作成を行います。実装が完了したら、動作確認をします。「npm start」でサーバーが起動することを確認します。動作確認ができたら、コミットします。「git add .」「git commit -m 'プロジェクト初期設定完了'」という操作です。これで1タスク1コミットが完了です。次にtasks.mdに戻って、完了したタスクのチェックボックスにチェックを入れます。「@docs/tasks.md のプロジェクト初期設定タスクを完了にしてください」と指示するだけで更新してくれます。このサイクル、つまり、設計書を@インポートで参照→タスクリストの次のタスクを指示→Claude Codeが実装→動作確認→コミット→タスクリスト更新→次のタスクへ、を繰り返すことで、プロジェクトが着実に完成に近づいていきます。docsフォルダのrequirements.md・design.md・tasks.mdの3ファイルが、プロジェクトの地図であり、Claude Codeへの指示の根拠になります。</t>
         </is>
@@ -5479,12 +5482,12 @@
           <t>まとめ</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>・スライド「まとめ」へ切り替える。・スライドの要点を、講師が口頭でも繰り返す。</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>では、この動画をまとめます。設計書は「どう作るか」を定義するもので、技術スタック・ディレクトリ構成・画面遷移図・データモデル・API設計の5項目が基本構成です。「@docs/requirements.md の要件定義を読んで設計書を作成して」という指示ひとつで自動生成できます。タスクリストは設計書の内容を「10分から30分で完了できる単位」に分解したチェックリストです。1タスク1コミットのルールで、問題が起きた時に安全に戻れる仕組みを確保します。スペック駆動開発のサイクルは、設計書参照→タスク指示→実装→動作確認→コミット→更新→次のタスク、の繰り返しです。次の動画では、エラーが起きた時の対処とコードレビューの方法を学びます。</t>
         </is>
@@ -5511,12 +5514,12 @@
           <t>クロージング</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>・スライドは「まとめ」のまま。・講師が笑顔でカメラに向かって話す。</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>お疲れ様でした。設計書とタスクリストの自動生成、そして1タスク1コミットのサイクル、いかがでしたか？最初は「こんなに手順があるの？」と感じるかもしれませんが、一度このサイクルを覚えてしまえば、どんなプロジェクトでも同じパターンで進められます。配布資料の設計書テンプレートも参考にしてください。次の動画ではエラー対処とコードレビューを学びます。スペック駆動開発の仕上げです。それでは、次の動画でお会いしましょう。</t>
         </is>
@@ -6137,12 +6140,12 @@
           <t>切替</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>・スライド「表紙」を表示する。・講師は笑顔で画面中央に向かって立つ。</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>皆さん、こんにちは。セクション5の最後の動画です。お疲れ様でした。今日は、開発中に必ず直面するエラーへの対処方法と、コードの品質を保つためのレビュー機能についてお話しします。どんなに丁寧に開発を進めても、エラーは必ず起きます。でも、そのエラーをどう対処するかを知っていれば、怖くありません。この動画の後半では、Codexという新しいツールの紹介もします。Claude Codeがさらに進化した形のツールです。では始めていきましょう。</t>
         </is>
@@ -6169,12 +6172,12 @@
           <t>導入</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>・スライド「エラー対処の流れ」へ移行する。・3ステップを図で示しながら説明する。</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>まず、エラー対処の基本についてお話しします。エラーが出た時、皆さんはどう対応しますか？エラーメッセージを見て「何が書いてあるかわからない」と諦めてしまう方も多いと思います。でも、Claude Codeを使えば、エラーメッセージの解読から修正まで、AIが行ってくれます。エラー対処の流れは3ステップです。ステップ1は、エラーの内容をClaude Codeに伝えることです。ステップ2は、Claude Codeが原因を分析して修正を提案することです。ステップ3は、修正内容を確認して適用することです。このシンプルなサイクルで、ほとんどのエラーに対処できます。重要なポイントは、エラーメッセージをそのままコピペして渡すということです。自分でエラーの原因を推測して整理してから伝えようとしなくていいのです。余計な推測を加えない方が、AIは的確に判断できます。</t>
         </is>
@@ -6201,12 +6204,12 @@
           <t>概念説明</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>・スライド「エラー対処の流れ」のまま。・エラーの連続についても説明する。</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>エラー対処で覚えておいてほしいのが、ひとつ直すと別のエラーが出る、という現象です。これは、プログラム開発ではごく一般的なことです。あるエラーを修正すると、それに関連した別の部分で問題が表面化する、ということが起きます。こういった連続エラーが起きても同じアプローチで対処できます。エラーメッセージをそのまま渡す、Claude Codeが修正を提案する、確認して適用する、のサイクルを繰り返せばいいのです。もし何度も同じ種類のエラーが繰り返される場合は、「根本原因を調査して、設計レベルでの改善を提案してください」と伝えてみてください。表面的な修正ではなく、本質的な解決策を提示してくれます。そして、1タスク1コミットのルールがここで活きてきます。エラーが修正できない深刻な状況になっても、直前のコミットの状態に戻すことができます。安全ネットが常にあるのです。</t>
         </is>
@@ -6233,12 +6236,12 @@
           <t>実演①</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>・ターミナル画面「エラー対処実演」へ切り替える。・実際のエラーと修正の過程を見せる。</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>では、エラー対処の実演をします。サンプルのコードをわざとエラーが出る状態にしてあります。サーバーを起動してみます。「npm start」と入力します。すると赤いエラーメッセージが出ます。「Cannot find module 'express'」というメッセージです。このエラーメッセージ、英語でわかりにくいですよね。でも、これをそのままClaude Codeに渡すだけです。「npm startを実行したら以下のエラーが出ました。修正してください。Cannot find module 'express'」とメッセージを送ります。するとClaude Codeが「expressモジュールがインストールされていないためです。npm install expressを実行してください」と回答して、さらに自動的にコマンドを実行してくれます。インストールが完了したら、再度「npm start」を実行します。今度はサーバーが正常に起動しました。次に、もう少し複雑なエラーも試してみましょう。意図的にコードの一部を壊します。今度は「TypeError: Cannot read properties of undefined」というエラーが出ます。このエラーもそのまま渡します。するとClaude Codeが、どの変数がundefinedになっているかを特定して、修正コードを提示してくれます。提示された修正を確認してOKであれば適用します。これがエラー対処の基本サイクルです。</t>
         </is>
@@ -6265,12 +6268,12 @@
           <t>コードレビュー説明</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>・スライド「コードレビューの概要」へ移行する。・/simplifyと/reviewの違いを図で示す。</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>次に、コードレビュー機能についてお話しします。コードレビューとは、書いたコードをチェックして品質を確認する作業のことです。Claude Codeには2つのレビュー関連のコマンドがあります。1つめが/simplifyです。これは、既存のコードをよりシンプルで効率的な形に書き直す提案をする機能です。例えば、20行で書いていたコードが5行で書けると提示してくれたり、繰り返しの多い処理を関数にまとめる提案をしてくれたりします。AIが生成したコードは動くけれど少し冗長なことがあります。その仕上げとして/simplifyが特に効果的です。2つめが/reviewです。これは、プルリクエストの変更内容をレビューする機能です。潜在的な問題点、セキュリティリスク、パフォーマンスの懸念、コーディング規約違反を指摘してくれます。プロのエンジニアによるコードレビューと同じ視点でフィードバックが返ってきます。</t>
         </is>
@@ -6297,12 +6300,12 @@
           <t>実演②③</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>・ターミナル画面「/simplify実演」と「/review実演」へ切り替えながら実演する。</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>では、/simplifyと/reviewの実演をします。まず/simplifyです。先ほど実装したコードに対して/simplifyコマンドを実行します。Claude Codeが「この関数は3行に縮められます」「このif文はオプショナルチェーンで書けます」「このループはArray.filterとArray.mapで置き換えられます」といった提案を返してきます。各提案に対して、採用するかどうかを判断して適用していきます。提案をすべて採用する必要はありません。コードが読みやすくなる提案を選んで適用するのがいいでしょう。次に/reviewです。GitHubのプルリクエストを作成して、/reviewコマンドを使ってみます。するとClaude Codeが、「入力値のバリデーションが不足しています」「エラーハンドリングが欠如しています」「変数名がわかりにくいです」「SQLインジェクションの脆弱性があります」といった指摘を返してきます。これはプロのエンジニアが行うコードレビューと同等の内容です。指摘された項目を修正することで、コードの品質が大幅に向上します。特にセキュリティ関連の指摘は見落としやすいので、/reviewを使って必ず確認する習慣をつけると良いでしょう。</t>
         </is>
@@ -6329,12 +6332,12 @@
           <t>Codex紹介</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>・スライド「Codex紹介」へ切り替える。・Codexの特徴を図で説明する。</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>最後に、Codexというツールを紹介します。CodexはAnthropicが提供するクラウドベースのコーディングエージェントです。Claude Codeをさらに進化させたツールで、タスクを非同期で処理できます。Claude Codeは基本的に、皆さんがターミナルの前に座っている間に作業してくれます。Codexはそれよりさらに進んで、「このタスクをやっておいて」と指示したら、皆さんが他の作業をしている間にバックグラウンドで進めてくれます。具体的にはサンドボックス環境でコードの修正、テストの実行、プルリクエストの作成までを自動で行ってくれます。複数のタスクを並行処理することも可能です。現時点では、Claude CodeのほうがCodexより使いやすい場面も多くあります。ですが、これからAIコーディングツールがどういう方向に進化していくかを知るためにも、Codexを知っておくことは価値があります。機会があればぜひ試してみてください。</t>
         </is>
@@ -6361,12 +6364,12 @@
           <t>まとめ</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>・スライド「まとめ」へ切り替える。・スライドの要点を、講師が口頭でも繰り返す。</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>では、この動画をまとめます。エラー対処は3ステップです。エラーメッセージをそのままClaude Codeに渡す、修正提案を受け取る、確認して適用する。自分でエラーを解読しようとせず、そのままコピペで渡すのがコツです。連続エラーが起きても同じアプローチで対処できます。深刻な場合は「根本原因を設計レベルで改善して」と伝えましょう。/simplifyはコードをよりシンプルに書き直す提案、/reviewはプルリクエストのコード品質チェックです。この2つをセットで使うことで、AIが生成したコードを洗練させられます。Codexは非同期でタスクを処理するClaudeの進化系ツールです。そしてセクション5全体を通して、スペック駆動開発の全体フローを学びました。GitHub・@インポート・スペック駆動・要件定義・設計書・タスクリスト・実装・エラー対処・コードレビュー、この一気通貫の流れが、実務レベルの開発フローです。</t>
         </is>
@@ -6393,12 +6396,12 @@
           <t>クロージング</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>・スライドは「まとめ」のまま。・講師が笑顔でカメラに向かって話す。</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>お疲れ様でした。セクション5、完走できましたね。本当にお疲れ様でした。GitHubの基礎から始まって、スペック駆動開発の全フローまで、かなり内容が濃かったと思います。最初は「こんなに手順があるの？」と思われたかもしれませんが、このフローを一度身につければ、どんなプロジェクトでも同じパターンで進められます。エラーが出ても怖くない、コードが複雑になっても管理できる、そういう自信が皆さんの中に育っているはずです。次のセクションでは、さらに実践的な内容に進んでいきます。一緒に頑張りましょう。それでは、次のセクションでお会いしましょう。</t>
         </is>
